--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128889093</v>
+        <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,17 +722,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan SV, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507717</v>
+        <v>507759</v>
       </c>
       <c r="R2" t="n">
-        <v>6310624</v>
+        <v>6310516</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,63 +788,65 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128889093</t>
+          <t>https://artportalen.se/Sighting/136899612</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124350795</v>
+        <v>128889093</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Magersryd, Sm</t>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507952</v>
+        <v>507717</v>
       </c>
       <c r="R3" t="n">
-        <v>6310311</v>
+        <v>6310624</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:12</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,33 +884,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ellen Flygare</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Flygare</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124350795</t>
+          <t>https://artportalen.se/Sighting/128889093</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72561755</v>
+        <v>124350795</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,16 +919,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,35 +941,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+          <t>Magersryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507601</v>
+        <v>507952</v>
       </c>
       <c r="R4" t="n">
-        <v>6310748</v>
+        <v>6310311</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,12 +982,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,55 +1012,71 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Ellen Flygare</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72561755</t>
+          <t>https://artportalen.se/Sighting/124350795</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127322100</v>
+        <v>72561755</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1106,12 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,13 +1145,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127322100</t>
+          <t>https://artportalen.se/Sighting/72561755</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128889126</v>
+        <v>127322100</v>
       </c>
       <c r="B6" t="n">
         <v>58114</v>
@@ -1178,14 +1186,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507717</v>
+        <v>507601</v>
       </c>
       <c r="R6" t="n">
-        <v>6310624</v>
+        <v>6310748</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,12 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,68 +1251,55 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128889126</t>
+          <t>https://artportalen.se/Sighting/127322100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66910171</v>
+        <v>128889126</v>
       </c>
       <c r="B7" t="n">
-        <v>58817</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+          <t>Bergalyckan s, Råsarna  Holmahult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507601</v>
+        <v>507717</v>
       </c>
       <c r="R7" t="n">
-        <v>6310748</v>
+        <v>6310624</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,16 +1357,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66910171</t>
+          <t>https://artportalen.se/Sighting/128889126</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100958384</v>
+        <v>66910171</v>
       </c>
       <c r="B8" t="n">
-        <v>56884</v>
+        <v>58817</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1401,14 +1396,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,12 +1445,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2017-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,7 +1459,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,16 +1476,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100958384</t>
+          <t>https://artportalen.se/Sighting/66910171</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66910345</v>
+        <v>100958384</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>56884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,31 +1493,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223597</v>
+        <v>208255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
@@ -1556,17 +1560,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-07-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Både blommande och överblommade.</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,6 +1574,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1591,6 +1591,120 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100958384</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>66910345</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergalyckan 100m S, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>507601</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6310748</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-07-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Både blommande och överblommade.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66910345</t>
         </is>
@@ -1606,6 +1720,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1707,6 +1707,117 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66910345</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137331300</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergalyckan SV, Råsarna  Holmahult, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>507759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6310516</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dädesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Några dm2</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137331300</t>
         </is>
       </c>
     </row>
@@ -1721,6 +1832,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79197</v>
+        <v>79200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79200</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79205</v>
+        <v>79216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79216</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136899612</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>79219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26127-2024 artfynd.xlsx
+++ b/artfynd/A 26127-2024 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>137331300</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
